--- a/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-high-level-summary.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-high-level-summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,165 +446,145 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>torch:test/image_F1Score_mean</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/image_F1Score_std</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/iter_time_mean</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/iter_time_std</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/latency_mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/latency_std</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/e2e_time_mean</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/e2e_time_std</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/image_F1Score_mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/image_F1Score_std</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/latency_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/latency_std</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/e2e_time_mean</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/e2e_time_std</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/image_F1Score_mean</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/image_F1Score_std</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/latency_mean</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/latency_std</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/e2e_time_mean</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/e2e_time_std</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>training:epoch_mean</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>training:epoch_std</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>training:e2e_time_mean</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>training:e2e_time_std</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>training:gpu_mem_mean</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>training:gpu_mem_std</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>training:train/iter_time_mean</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>training:train/iter_time_std</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>torch:test/image_F1Score_mean</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>torch:test/image_F1Score_std</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>torch:test/iter_time_mean</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>torch:test/iter_time_std</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>torch:test/latency_mean</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>torch:test/latency_std</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>torch:test/e2e_time_mean</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>torch:test/e2e_time_std</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>optimize:test/image_F1Score_mean</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>optimize:test/image_F1Score_std</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>optimize:test/iter_time_mean</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>optimize:test/iter_time_std</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>optimize:test/latency_mean</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>optimize:test/latency_std</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>optimize:test/e2e_time_mean</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>optimize:test/e2e_time_std</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>export:test/image_F1Score_mean</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>export:test/image_F1Score_std</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>export:test/iter_time_mean</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>export:test/iter_time_std</t>
-        </is>
-      </c>
       <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>export:test/latency_mean</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>export:test/latency_std</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>export:test/e2e_time_mean</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>export:test/e2e_time_std</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
@@ -627,102 +607,90 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.8254</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>19.7366</v>
+        <v>0.2429</v>
       </c>
       <c r="G2" t="n">
-        <v>10.6375</v>
+        <v>0.0522</v>
       </c>
       <c r="H2" t="n">
-        <v>0.916</v>
+        <v>0.0136</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0265</v>
+        <v>0.0034</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0885</v>
+        <v>5.627</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0644</v>
+        <v>0.7085</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8305</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0678</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3607</v>
+        <v>0.0438</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0074</v>
+        <v>0.0021</v>
       </c>
       <c r="P2" t="n">
-        <v>0.017</v>
+        <v>19.151</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0014</v>
+        <v>4.9576</v>
       </c>
       <c r="R2" t="n">
-        <v>7.2581</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1095</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4079</v>
+        <v>0.0561</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4074</v>
+        <v>0.0016</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0594</v>
+        <v>24.4434</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0046</v>
+        <v>5.8605</v>
       </c>
       <c r="X2" t="n">
-        <v>0.068</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0039</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>29.7819</v>
+        <v>20.0072</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.172599999999999</v>
+        <v>11.1191</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.9126</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0767</v>
+        <v>0.0244</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0711</v>
+        <v>0.1818</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.0798</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>34.7607</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>8.4125</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
+        <v>0.021</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>ANOMALY</t>
         </is>
@@ -745,102 +713,196 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.0286</v>
+        <v>0.8528</v>
       </c>
       <c r="E3" t="n">
-        <v>0.169</v>
+        <v>0.061</v>
       </c>
       <c r="F3" t="n">
-        <v>67.1677</v>
+        <v>0.2297</v>
       </c>
       <c r="G3" t="n">
-        <v>43.992</v>
+        <v>0.0519</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7631</v>
+        <v>0.013</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0293</v>
+        <v>0.0033</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0883</v>
+        <v>5.3484</v>
       </c>
       <c r="K3" t="n">
-        <v>0.063</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8012</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1091</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2182</v>
+        <v>0.0367</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0896</v>
+        <v>0.0024</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0125</v>
+        <v>16.0416</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0033</v>
+        <v>4.3821</v>
       </c>
       <c r="R3" t="n">
-        <v>5.2778</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3326</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4923</v>
+        <v>0.047</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3685</v>
+        <v>0.0018</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0549</v>
+        <v>20.5122</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0054</v>
+        <v>5.167</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0645</v>
+        <v>29.5143</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0046</v>
+        <v>19.746</v>
       </c>
       <c r="Z3" t="n">
-        <v>28.2611</v>
+        <v>350.9514</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.9015</v>
+        <v>166.5532</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.772</v>
+        <v>1.6334</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.116</v>
+        <v>0.0478</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0644</v>
+        <v>0.1356</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0041</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.07340000000000001</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>32.0425</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>8.051500000000001</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
+        <v>0.0757</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8212</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0762</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7.9558</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.4098</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P4" t="n">
+        <v>30.9912</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6.6497</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.0803</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="V4" t="n">
+        <v>34.8818</v>
+      </c>
+      <c r="W4" t="n">
+        <v>8.4483</v>
+      </c>
+      <c r="X4" t="n">
+        <v>199</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2800.1242</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2428.4389</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>6.2863</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.2239</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>ANOMALY</t>
         </is>
